--- a/data/trans_orig/IP2004-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP2004-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3224</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11281</t>
+          <t>11906</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9498</t>
+          <t>9758</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6935</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17910</t>
+          <t>17676</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76249</t>
+          <t>75624</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>84306</t>
+          <t>84049</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>72596</t>
+          <t>72336</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80097</t>
+          <t>80080</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>151715</t>
+          <t>151949</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>162690</t>
+          <t>162935</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>96,06%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7792</t>
+          <t>7755</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18863</t>
+          <t>19208</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10816</t>
+          <t>10453</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23703</t>
+          <t>23746</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21668</t>
+          <t>21370</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37909</t>
+          <t>38642</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>375453</t>
+          <t>375108</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>386524</t>
+          <t>386561</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>427477</t>
+          <t>427434</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>440364</t>
+          <t>440727</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>807587</t>
+          <t>806854</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>823828</t>
+          <t>824126</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>744</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7617</t>
+          <t>7545</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>788</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7734</t>
+          <t>7589</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>153699</t>
+          <t>153771</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>160532</t>
+          <t>160572</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>300285</t>
+          <t>300430</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>307226</t>
+          <t>307231</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15475</t>
+          <t>15021</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30106</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14335</t>
+          <t>15694</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29172</t>
+          <t>30303</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34351</t>
+          <t>33704</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54324</t>
+          <t>55602</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>612709</t>
+          <t>613056</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>627687</t>
+          <t>628141</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>650805</t>
+          <t>649674</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>665642</t>
+          <t>664283</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1268816</t>
+          <t>1267538</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1288789</t>
+          <t>1289436</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,45%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1491</t>
+          <t>1429</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8436</t>
+          <t>8440</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2422</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11555</t>
+          <t>11304</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>5658</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16962</t>
+          <t>17345</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80323</t>
+          <t>80319</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>87268</t>
+          <t>87330</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>71070</t>
+          <t>71321</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80203</t>
+          <t>80020</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>154422</t>
+          <t>154039</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>165623</t>
+          <t>165726</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,7%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7675</t>
+          <t>7893</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20528</t>
+          <t>20256</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,82 +2694,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,84%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>10067</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>5322</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>16840</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>3,64%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>22977</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>16127</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>32804</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>2,61%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>1,83%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,91%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>10067</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>5685</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>16533</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>3,57%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>22977</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>15626</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>31864</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>397837</t>
+          <t>398109</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>410690</t>
+          <t>410472</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,82 +2807,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>98,11%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>452800</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>446027</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>457545</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>97,83%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>96,36%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>98,85%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1237</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>858255</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>848428</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>865105</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>97,39%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>96,28%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>98,17%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>452800</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>446334</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>457182</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,83%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>96,43%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>98,77%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1237</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>858255</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>849368</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>865606</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>97,39%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>96,38%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8429</t>
+          <t>8360</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3940</t>
+          <t>4414</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>2139</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9941</t>
+          <t>10243</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>146664</t>
+          <t>146733</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>153748</t>
+          <t>153582</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>152082</t>
+          <t>151608</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>301175</t>
+          <t>300873</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>309080</t>
+          <t>308977</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13929</t>
+          <t>14564</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29559</t>
+          <t>29592</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10797</t>
+          <t>11382</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25865</t>
+          <t>25529</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28324</t>
+          <t>28908</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49273</t>
+          <t>50162</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>632658</t>
+          <t>632625</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>648288</t>
+          <t>647653</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>675650</t>
+          <t>675986</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>690718</t>
+          <t>690133</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1314458</t>
+          <t>1313569</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1335407</t>
+          <t>1334823</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>796</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6822</t>
+          <t>7122</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>623</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5341</t>
+          <t>5930</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9442</t>
+          <t>9195</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49443</t>
+          <t>49143</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55495</t>
+          <t>55469</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62033</t>
+          <t>61444</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>66774</t>
+          <t>66751</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>114196</t>
+          <t>114443</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>121647</t>
+          <t>121620</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,37%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8671</t>
+          <t>8334</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21915</t>
+          <t>21128</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4623</t>
+          <t>4515</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14767</t>
+          <t>14831</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15770</t>
+          <t>15977</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31728</t>
+          <t>31339</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>418450</t>
+          <t>419237</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>431694</t>
+          <t>432031</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>449016</t>
+          <t>448952</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>459160</t>
+          <t>459268</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>872420</t>
+          <t>872809</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>888378</t>
+          <t>888171</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>540</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5699</t>
+          <t>5726</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4008</t>
+          <t>4370</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>710</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>7077</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>156309</t>
+          <t>156282</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>161462</t>
+          <t>161468</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>165730</t>
+          <t>165368</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>324282</t>
+          <t>324669</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>331041</t>
+          <t>331036</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12479</t>
+          <t>12574</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26752</t>
+          <t>27149</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6607</t>
+          <t>6782</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17323</t>
+          <t>17999</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21945</t>
+          <t>22538</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40238</t>
+          <t>40371</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>631885</t>
+          <t>631488</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>646158</t>
+          <t>646063</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>683572</t>
+          <t>682896</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>694288</t>
+          <t>694113</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1319294</t>
+          <t>1319161</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1337587</t>
+          <t>1336994</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>2536</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>837</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7163</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>943</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8398</t>
+          <t>8320</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51748</t>
+          <t>51163</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52640</t>
+          <t>52247</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58952</t>
+          <t>58966</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>105104</t>
+          <t>105182</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>112574</t>
+          <t>112559</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3099</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12914</t>
+          <t>13278</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5376</t>
+          <t>5213</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16197</t>
+          <t>16795</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10307</t>
+          <t>10265</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24987</t>
+          <t>24438</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>440503</t>
+          <t>440139</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>450318</t>
+          <t>450166</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>489386</t>
+          <t>488788</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>500207</t>
+          <t>500370</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>934014</t>
+          <t>934563</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>948694</t>
+          <t>948736</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6233,7 +6233,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>3565</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10648</t>
+          <t>10626</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2273</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11375</t>
+          <t>11347</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>143537</t>
+          <t>143973</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>171431</t>
+          <t>171453</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>318242</t>
+          <t>318270</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>327499</t>
+          <t>327344</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4010</t>
+          <t>4089</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14776</t>
+          <t>13569</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10934</t>
+          <t>10765</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26191</t>
+          <t>25750</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17266</t>
+          <t>16394</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34185</t>
+          <t>34711</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>639878</t>
+          <t>641085</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>650644</t>
+          <t>650565</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>721274</t>
+          <t>721715</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>736531</t>
+          <t>736700</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1367934</t>
+          <t>1367408</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1384853</t>
+          <t>1385725</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP2004-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP2004-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4798</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1948</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9222</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5,84%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>11,23%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>6635</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3481</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11906</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3294</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>11585</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>7,58%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>13,6%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4798</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>9758</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>5,84%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>6708</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17676</t>
+          <t>17057</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,06%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>77296</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>72872</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>80146</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>94,16%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>88,77%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,63%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>121</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>80895</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>75624</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>84049</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>75945</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>84236</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>92,42%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>86,4%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,02%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>77296</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>72336</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>80080</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>94,16%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>151949</t>
+          <t>152568</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>162935</t>
+          <t>162917</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,05%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>82094</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>82094</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>82094</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>131</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>87530</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>87530</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>87530</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>82094</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>82094</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>82094</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>16750</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>11101</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>23693</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,71%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5,25%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>12372</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>7755</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>19208</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>7668</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>20208</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>3,14%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,87%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>16750</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>10453</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>23746</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,71%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21370</t>
+          <t>21210</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38642</t>
+          <t>38539</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>434430</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>427487</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>440079</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,29%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>94,75%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,54%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>575</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>381944</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>375108</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>386561</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>374108</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>386648</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>96,86%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>95,13%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,03%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>654</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>434430</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>427434</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>440727</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,29%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>806854</t>
+          <t>806957</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>824126</t>
+          <t>824286</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,49%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>451180</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>451180</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>451180</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>594</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>394316</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>394316</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>394316</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>451180</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>451180</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>451180</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3043</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>744</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7545</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>736</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6988</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,89%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,46%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>733</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7589</t>
+          <t>7634</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -1522,74 +1522,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>146703</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>158273</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>153771</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>160572</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>154328</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>160580</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>98,11%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>95,32%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>95,67%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>99,54%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>146703</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>450</t>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>300430</t>
+          <t>300385</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>307231</t>
+          <t>307286</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>146703</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>146703</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>146703</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>161316</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>161316</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>161316</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>146703</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>146703</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>146703</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1757,67 +1757,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>21548</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>15087</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>29696</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,17%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,37%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>22051</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>15021</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>30106</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>15223</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>30597</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,43%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,34%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>21548</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>15694</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>30303</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33704</t>
+          <t>33813</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55602</t>
+          <t>54857</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>989</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>658429</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>650281</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>664890</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,83%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,63%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,78%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>927</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>621111</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>613056</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>628141</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>612565</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>627939</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>96,57%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,32%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,66%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>989</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>658429</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>649674</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>664283</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,83%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1267538</t>
+          <t>1268283</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1289436</t>
+          <t>1289327</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,44%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1022</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>679977</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>679977</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>679977</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>960</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>643162</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>643162</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>643162</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1022</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>679977</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>679977</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>679977</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5797</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10950</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7,02%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>13,25%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>4182</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1429</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8440</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1929</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8507</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>4,71%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,51%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5797</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2605</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>11304</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>7,02%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5658</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17345</t>
+          <t>16229</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>76828</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>71675</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>80490</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>92,98%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>86,75%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,42%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>84577</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>80319</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>87330</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>80252</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>86830</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>95,29%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>90,49%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,39%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>76828</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>71321</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>80020</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>92,98%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>154039</t>
+          <t>155155</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>165726</t>
+          <t>166345</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>97,06%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>82625</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>82625</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>82625</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>129</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>88759</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>88759</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>88759</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>82625</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>82625</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>82625</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,107 +2669,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>10067</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5902</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>16580</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,58%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>12910</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>7893</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>20256</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>8116</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>20414</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>3,09%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,84%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>10067</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>5322</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>16840</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
+          <t>4,88%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>22977</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>16158</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>32067</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>2,61%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>3,64%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>22977</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>16127</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>32804</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -2782,102 +2782,102 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>452800</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>446287</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>456965</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,83%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,42%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,72%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>587</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>405455</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>398109</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>410472</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>397951</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>410249</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>96,91%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>95,16%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,11%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>452800</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>446027</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>457545</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,83%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
+          <t>95,12%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>98,06%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1237</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>858255</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>849165</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>865074</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>97,39%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>96,36%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>98,85%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1237</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>858255</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>848428</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>865105</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>97,39%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>96,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>664</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>462867</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>462867</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>462867</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>605</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>418365</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>418365</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>418365</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>664</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>462867</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>462867</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>462867</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1255</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4449</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,85%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3864</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1511</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8360</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8935</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,49%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,39%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1255</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4414</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>2253</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10243</t>
+          <t>10627</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>154767</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>151573</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>156022</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,2%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,15%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>214</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>151229</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>146733</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>153582</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>146158</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>153688</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>97,51%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>94,61%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,03%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>154767</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>151608</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>156022</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,2%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>300873</t>
+          <t>300489</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>308977</t>
+          <t>308863</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>156022</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>156022</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>156022</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155093</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155093</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155093</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>156022</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>156022</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>156022</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>17120</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10987</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>25264</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>20955</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>14564</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>29592</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>14641</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>29159</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,16%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,47%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>17120</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>11382</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>25529</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28908</t>
+          <t>28630</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50162</t>
+          <t>50014</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>978</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>684395</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>676251</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>690528</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,56%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,4%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,43%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>924</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>641262</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>632625</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>647653</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>633058</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>647576</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>96,84%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,53%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,8%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>978</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>684395</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>675986</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>690133</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,56%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1313569</t>
+          <t>1313717</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1334823</t>
+          <t>1335101</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>701515</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>701515</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>701515</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>953</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>662217</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>662217</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>662217</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>701515</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>701515</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>701515</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1988</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5260</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,95%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7,81%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2857</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>796</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7122</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>752</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6623</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>5,08%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12,66%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1988</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>623</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5930</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>1832</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9195</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>65386</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>62114</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>66771</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,05%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>92,19%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,11%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>53408</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>49143</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>55469</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>49642</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>55513</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>94,92%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>87,34%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,59%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>65386</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>61444</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>66751</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,05%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>114443</t>
+          <t>114632</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>121620</t>
+          <t>121806</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,52%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>67374</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>67374</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>67374</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>56265</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>56265</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>56265</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>67374</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>67374</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>67374</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8748</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4745</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>15266</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,29%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>13732</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8334</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>21128</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>8899</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>21254</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>3,12%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,8%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>8748</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>4515</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>14831</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15977</t>
+          <t>15403</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31339</t>
+          <t>31660</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>455035</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>448517</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>459038</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,11%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,71%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,98%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>426633</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>419237</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>432031</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>419111</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>431466</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>96,88%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>95,2%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,11%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>455035</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>448952</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>459268</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,11%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>872809</t>
+          <t>872488</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>888171</t>
+          <t>888745</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,3%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>463783</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>463783</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>463783</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>662</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>440365</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>440365</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>440365</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>659</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>463783</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>463783</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>463783</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3547</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2002</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>540</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5726</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>544</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5978</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,24%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4370</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>837</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7077</t>
+          <t>7066</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>169025</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>166191</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>169738</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,58%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,91%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>239</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>160006</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>156282</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>161468</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>156030</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>161464</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>98,76%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>96,47%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,67%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>169025</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>165368</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>169738</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,58%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>324669</t>
+          <t>324680</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>331036</t>
+          <t>330909</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>169738</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>169738</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>169738</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>162008</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>162008</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>162008</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>169738</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>169738</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>169738</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11449</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6984</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>17556</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>18592</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>12574</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>27149</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>12341</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>26686</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,82%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,91%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,12%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>11449</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>6782</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>17999</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22538</t>
+          <t>21326</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40371</t>
+          <t>39957</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>984</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>689446</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>683339</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>693911</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,37%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,5%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>961</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>640045</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>631488</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>646063</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>631951</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>646296</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>97,18%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,88%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,09%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>984</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>689446</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>682896</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>694113</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,37%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1319161</t>
+          <t>1319575</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1336994</t>
+          <t>1338206</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,43%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>700895</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>700895</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>700895</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>988</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>658637</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>658637</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>658637</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>700895</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>700895</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>700895</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2886</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>878</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7523</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5,25%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>13,69%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2536</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2121</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,72%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2823</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>837</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7556</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,72%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3214</t>
+          <t>3226</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>954</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8320</t>
+          <t>8469</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -5645,74 +5645,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>52047</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>47410</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>54055</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>94,75%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>86,31%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,4%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>53308</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>51163</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>99,27%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>95,28%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>45565</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>43784</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>45905</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>99,26%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,38%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>56980</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>52247</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>58966</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>95,28%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>87,37%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>98,6%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>143</t>
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>110288</t>
+          <t>97612</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>105182</t>
+          <t>92369</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>112559</t>
+          <t>99884</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>54933</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>54933</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>54933</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>59803</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>59803</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>59803</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>113502</t>
+          <t>100838</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>113502</t>
+          <t>100838</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>113502</t>
+          <t>100838</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8478</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4811</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>15040</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,22%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>6567</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3251</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>13278</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9544</t>
+          <t>6844</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5213</t>
+          <t>3328</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16795</t>
+          <t>13431</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>16111</t>
+          <t>15321</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10265</t>
+          <t>9692</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24438</t>
+          <t>23586</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>458382</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>451820</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>462049</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,18%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,78%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,97%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>619</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>446850</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>440139</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>450166</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>98,55%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,07%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,28%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>618</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>496039</t>
+          <t>419269</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>488788</t>
+          <t>412682</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>500370</t>
+          <t>422785</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>942890</t>
+          <t>877652</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>934563</t>
+          <t>869387</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>948736</t>
+          <t>883281</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>466860</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>466860</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>466860</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>453417</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>453417</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>453417</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>631</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>505583</t>
+          <t>426113</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>505583</t>
+          <t>426113</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>505583</t>
+          <t>426113</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>959001</t>
+          <t>892973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>959001</t>
+          <t>892973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>959001</t>
+          <t>892973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4264</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1707</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9314</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,56%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>692</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3565</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3848</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4690</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1956</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>10626</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,22 +6293,22 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>5382</t>
+          <t>5035</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2273</t>
+          <t>2167</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11347</t>
+          <t>10175</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -6331,74 +6331,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>163132</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>158082</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>165689</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,45%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>94,44%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,98%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>224</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>146846</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>143973</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>147538</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>99,53%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,58%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>147529</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>144452</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>148300</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>99,48%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,41%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>177389</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>171453</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>180123</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,42%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>94,16%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>98,93%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>453</t>
@@ -6406,27 +6406,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>324235</t>
+          <t>310661</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>318270</t>
+          <t>305521</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>327344</t>
+          <t>313529</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>167396</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>167396</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>167396</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>147538</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>147538</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>147538</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>182079</t>
+          <t>148300</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>182079</t>
+          <t>148300</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>182079</t>
+          <t>148300</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>329617</t>
+          <t>315696</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>329617</t>
+          <t>315696</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>329617</t>
+          <t>315696</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15627</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10377</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>23077</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,35%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>7651</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>4089</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>13569</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>7955</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3858</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>13843</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,62%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>17057</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>10765</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>25750</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>24707</t>
+          <t>23583</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16394</t>
+          <t>16571</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34711</t>
+          <t>33984</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -6674,74 +6674,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>924</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>673563</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>666113</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>678813</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,73%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,65%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,49%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>909</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>647003</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>641085</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>650565</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>98,83%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,93%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>612362</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>606474</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>616459</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>98,72%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,77%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,38%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>924</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>730408</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>721715</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>736700</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,72%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>96,56%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>98,56%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1833</t>
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1377412</t>
+          <t>1285924</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1367408</t>
+          <t>1275523</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1385725</t>
+          <t>1292936</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>946</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>689190</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>689190</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>689190</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>920</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>654654</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>654654</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>654654</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>946</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>747465</t>
+          <t>620317</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>747465</t>
+          <t>620317</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>747465</t>
+          <t>620317</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1402119</t>
+          <t>1309507</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1402119</t>
+          <t>1309507</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1402119</t>
+          <t>1309507</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
